--- a/SLR/Full-Paper-Read/Paper-Review/PS14.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS14.xlsx
@@ -11,24 +11,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment authorId="0" ref="I2">
-      <text>
-        <t xml:space="preserve">PS14 presents a systematic mapping study on automated analysis of feature models (AAFM).
-	-Adnan Ashraf</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -42,103 +26,72 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">The paper focuses on Automated Analysis of Feature Models (AAFM) and provides an overview of the evolution of this field since 2010 by performing a systematic mapping study. Among the emerged research opportunities: 
-- An emerging challenge in this area is the configuration of a diversity of distributed Software Product Line (SPL) descriptions, sometimes known as software </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>ecosystems</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t xml:space="preserve">. As SPLs grow, configuring and maintaining them become an unfeasible task for a small group. Also, different stakeholders and privacy policies encourage the use of visibility restrictions for the configurable parts. We think that there is still work to be done in this area like, for example, to enable the parallel configuration of those open and distributed SPLs.
-- The number of different scenarios where AAFM can be applied have been proved to be very large and we envision that there will be more and more scenarios where it will be applied in the future. </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <b/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>Ecosystems</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Arial"/>
-        <i/>
-        <color theme="1"/>
-        <sz val="10.0"/>
-      </rPr>
-      <t>, cyber-physical systems, robotics, big data or the internet of the things are only some examples where variability is a first-class citizen and can use AAFM techniques in their development.</t>
-    </r>
-  </si>
-  <si>
-    <t>This paper is partially out of scope but, among the research opportunities identified,  the authors mention ecosystems and the variability as challenge</t>
+    <t>we report on our experience in developing the AMASS open source ecosystem. This ecosystem includes (1) an open source tool platform that supports the main CPS assurance and certification activities, (2) external tools with added-value features, and (3) an open community of developers and users. The platform integrates existing solutions for system modelling, process engineering, and compliance and argumentation management. We also present the application of the AMASS tool platform in 11 industrial case studies from five different application domains. The results show that the platform is a feasible means for CPS assurance and certification and that practitioners find benefits in assurance-oriented system modelling and in integrated system assurance information, among other areas. Nonetheless, improvement opportunities also exist, most notably regarding tool interoperability and usability.</t>
+  </si>
+  <si>
+    <t>I guess we should also include this paper in related work somehow?
+Also, we can probably get inspired from their related work section
+Worth highlighting being based on Eclipse</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
+    <t>&gt;5</t>
+  </si>
+  <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
-    <t>N</t>
+    <t>Y</t>
   </si>
   <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
-    <t>Modeling and Model-Driven Engineering</t>
+    <t>n.a.</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature models, variability </t>
+    <t>assurance and certification processes</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
+    <t xml:space="preserve">the ecosystem has been developed in the scope of a research project between industry and academia, including potential users of the AMASS tool platform. </t>
+  </si>
+  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Aerospace</t>
+  </si>
+  <si>
+    <t>Railway</t>
+  </si>
+  <si>
+    <t>Digital Life</t>
+  </si>
+  <si>
     <t>Application Domain Independent</t>
+  </si>
+  <si>
+    <t>Avionics, Digital Automation</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
@@ -505,11 +458,13 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -517,13 +472,11 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
@@ -617,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="55">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -631,7 +584,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -646,47 +599,35 @@
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf borderId="16" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="15" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="17" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="17" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -733,6 +674,9 @@
     <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
@@ -741,6 +685,9 @@
     </xf>
     <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -1005,7 +952,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="2.5"/>
-    <col customWidth="1" min="2" max="2" width="62.38"/>
+    <col customWidth="1" min="2" max="2" width="45.13"/>
     <col customWidth="1" min="3" max="3" width="9.0"/>
     <col customWidth="1" min="4" max="4" width="9.88"/>
     <col customWidth="1" min="5" max="5" width="9.0"/>
@@ -1052,7 +999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="82.5" customHeight="1">
+    <row r="3" ht="157.5" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1070,8 +1017,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17">
-        <v>0.0</v>
+      <c r="C4" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1079,7 +1026,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1087,18 +1034,18 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
-      <c r="I5" s="21" t="s">
-        <v>7</v>
+      <c r="I5" s="19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1106,27 +1053,27 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="21" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1137,35 +1084,35 @@
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="C7" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
       <c r="H7" s="18"/>
-      <c r="I7" s="26" t="s">
-        <v>7</v>
+      <c r="I7" s="21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16">
         <v>6.0</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="21" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="26" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1175,16 +1122,16 @@
       <c r="B9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
+      <c r="C9" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="21" t="s">
-        <v>7</v>
+      <c r="I9" s="19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1194,26 +1141,26 @@
       <c r="B10" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>7</v>
+      <c r="D10" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="27" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1221,30 +1168,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="32">
+        <v>26</v>
+      </c>
+      <c r="C11" s="28">
         <f>Quality!C29</f>
-        <v>10</v>
-      </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="21" t="s">
-        <v>7</v>
+        <v>9.62962963</v>
+      </c>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="33" t="s">
-        <v>22</v>
+      <c r="B14" s="29" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="33" t="s">
-        <v>23</v>
+      <c r="B15" s="29" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2284,8 +2231,7 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2304,362 +2250,362 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
+      <c r="A1" s="30"/>
+      <c r="B1" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="32"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="34"/>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="41">
+      <c r="A2" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="37">
         <v>1.0</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="42"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="41">
+      <c r="A3" s="39"/>
+      <c r="B3" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="37">
         <v>1.0</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="42"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="38"/>
     </row>
     <row r="4">
-      <c r="A4" s="43"/>
-      <c r="B4" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="41">
+      <c r="A4" s="39"/>
+      <c r="B4" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="37">
         <v>1.0</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
     </row>
     <row r="5">
-      <c r="A5" s="43"/>
-      <c r="B5" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="41">
+      <c r="A5" s="39"/>
+      <c r="B5" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="37">
         <v>1.0</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
     </row>
     <row r="6">
-      <c r="A6" s="43"/>
-      <c r="B6" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="41">
+      <c r="A6" s="39"/>
+      <c r="B6" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="37">
         <v>1.0</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7">
-      <c r="A7" s="44"/>
-      <c r="B7" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="41">
+      <c r="A7" s="40"/>
+      <c r="B7" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="37">
         <v>1.0</v>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="41">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="41">
         <f>(SUM(C2:C7)/D7)*10</f>
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="48">
+      <c r="A8" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="44">
         <v>1.0</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9">
-      <c r="A9" s="43"/>
-      <c r="B9" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="48">
+      <c r="A9" s="39"/>
+      <c r="B9" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="44">
         <v>1.0</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
     </row>
     <row r="10">
-      <c r="A10" s="43"/>
-      <c r="B10" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="48">
+      <c r="A10" s="39"/>
+      <c r="B10" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="44">
         <v>1.0</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
     </row>
     <row r="11">
-      <c r="A11" s="43"/>
-      <c r="B11" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="48">
+      <c r="A11" s="39"/>
+      <c r="B11" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="44">
         <v>1.0</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
     </row>
     <row r="12">
-      <c r="A12" s="43"/>
-      <c r="B12" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="48">
+      <c r="A12" s="39"/>
+      <c r="B12" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="45">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="39"/>
+      <c r="B13" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="44">
         <v>1.0</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="43"/>
-      <c r="B13" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="48">
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="39"/>
+      <c r="B14" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="44">
         <v>1.0</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="43"/>
-      <c r="B14" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="48">
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="39"/>
+      <c r="B15" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="44">
         <v>1.0</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="43"/>
-      <c r="B15" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="48">
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="39"/>
+      <c r="B16" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="44">
         <v>1.0</v>
       </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="43"/>
-      <c r="B16" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="48">
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="39"/>
+      <c r="B17" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="44">
         <v>1.0</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="43"/>
-      <c r="B17" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="48">
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="39"/>
+      <c r="B18" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="44">
         <v>1.0</v>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="43"/>
-      <c r="B18" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="48">
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40"/>
+      <c r="B19" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="44">
         <v>1.0</v>
       </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="44"/>
-      <c r="B19" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="45">
+      <c r="D19" s="41">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="41">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>10</v>
+        <v>9.583333333</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="51">
+      <c r="A20" s="46" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="48">
         <v>1.0</v>
       </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
     </row>
     <row r="21">
-      <c r="A21" s="43"/>
-      <c r="B21" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="51">
+      <c r="A21" s="39"/>
+      <c r="B21" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="48">
         <v>1.0</v>
       </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
     </row>
     <row r="22">
-      <c r="A22" s="43"/>
-      <c r="B22" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="51">
+      <c r="A22" s="39"/>
+      <c r="B22" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="48">
         <v>1.0</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
     </row>
     <row r="23">
-      <c r="A23" s="43"/>
-      <c r="B23" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="51">
+      <c r="A23" s="39"/>
+      <c r="B23" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="49">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="38"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="39"/>
+      <c r="B24" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="48">
         <v>1.0</v>
       </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="42"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="43"/>
-      <c r="B24" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="51">
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="38"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40"/>
+      <c r="B25" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="48">
         <v>1.0</v>
       </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="42"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="44"/>
-      <c r="B25" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="51">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="52">
+      <c r="D25" s="50">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="52">
+      <c r="E25" s="50">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>10</v>
-      </c>
-      <c r="F25" s="42"/>
+        <v>9.166666667</v>
+      </c>
+      <c r="F25" s="38"/>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="54" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="55">
+      <c r="A26" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="53">
         <v>1.0</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="42"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="38"/>
     </row>
     <row r="27">
-      <c r="A27" s="43"/>
-      <c r="B27" s="54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="55">
+      <c r="A27" s="39"/>
+      <c r="B27" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="53">
         <v>1.0</v>
       </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="42"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="38"/>
     </row>
     <row r="28">
-      <c r="A28" s="44"/>
-      <c r="B28" s="54" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="55">
+      <c r="A28" s="40"/>
+      <c r="B28" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="53">
         <v>1.0</v>
       </c>
-      <c r="D28" s="52">
+      <c r="D28" s="50">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="52">
+      <c r="E28" s="50">
         <f>(SUM(C26:C28)/D28)*10</f>
         <v>10</v>
       </c>
-      <c r="F28" s="42"/>
+      <c r="F28" s="38"/>
     </row>
     <row r="29">
-      <c r="B29" s="56">
+      <c r="B29" s="54">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="54">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>10</v>
+        <v>9.62962963</v>
       </c>
     </row>
   </sheetData>
